--- a/Statistics/1500m Fri_statistics.xlsx
+++ b/Statistics/1500m Fri_statistics.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17.13,75</t>
+          <t>17.13,81</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -655,7 +655,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2287,12 +2287,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21.20,86</t>
+          <t>21.19,52</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2322,12 +2322,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21.19,52</t>
+          <t>21.20,86</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gunnleif Nielsen</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21.38,12</t>
+          <t>21.37,71</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>02.03.2018</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Gunnleif Nielsen</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21.37,71</t>
+          <t>21.38,12</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>02.03.2018</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3439,12 +3439,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Ylva S. Dyngeland</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18.39,59</t>
+          <t>18.39,57</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05.06.2010</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3474,12 +3474,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ylva S. Dyngeland</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.39,57</t>
+          <t>18.39,59</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>05.06.2010</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/Statistics/1500m Fri_statistics.xlsx
+++ b/Statistics/1500m Fri_statistics.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17.13,81</t>
+          <t>17.13,75</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -655,7 +655,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1027,12 +1027,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Johan Hjelseth Storstad</t>
+          <t>Sebastian Amundsen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17.42,10</t>
+          <t>17.42,75</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1062,12 +1062,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sebastian Amundsen</t>
+          <t>Johan Hjelseth Storstad</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.42,75</t>
+          <t>17.42,10</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1762,12 +1762,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19.03,10</t>
+          <t>19.03,53</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31.10.2016</t>
+          <t>21.10.2022</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19.03,53</t>
+          <t>19.03,10</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21.10.2022</t>
+          <t>31.10.2016</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2252,12 +2252,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21.20,86</t>
+          <t>21.19,52</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2287,12 +2287,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21.19,52</t>
+          <t>21.20,86</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Gunnleif Nielsen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21.37,71</t>
+          <t>21.38,12</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>02.03.2018</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gunnleif Nielsen</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21.38,12</t>
+          <t>21.37,71</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>02.03.2018</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2567,12 +2567,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22.33,80</t>
+          <t>22.34,60</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2602,12 +2602,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22.34,60</t>
+          <t>22.33,80</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2855,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,33 +3283,103 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Edvin Grenne Spangelo</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20.50,82</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>337</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fredrik Holberg</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22.08,87</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>281</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Håkon Emil Øien</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>25.07,61</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C15" t="n">
         <v>192</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>13.04.2013</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Namsos</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>50m</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3439,12 +3509,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ylva S. Dyngeland</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18.39,57</t>
+          <t>18.39,59</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3452,12 +3522,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>05.06.2010</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3474,12 +3544,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Ylva S. Dyngeland</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.39,59</t>
+          <t>18.39,57</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3487,12 +3557,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05.06.2010</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4917,7 +4987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5170,25 +5240,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21.14,00</t>
+          <t>20.40,85</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24.04.2009</t>
+          <t>06.06.2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5205,25 +5275,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21.23,99</t>
+          <t>21.14,00</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.04.2015</t>
+          <t>24.04.2009</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5240,16 +5310,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edle Lund</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22.13,46</t>
+          <t>21.23,99</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5275,25 +5345,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Edle Lund</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22.27,17</t>
+          <t>22.13,46</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29.08.2015</t>
+          <t>19.04.2015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5310,33 +5380,173 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Othelie Annette Høie</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22.27,17</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>318</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>29.08.2015</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Hege Solberg Jørgensen</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>23.03,26</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>294</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>19.04.2015</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Namsos</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>50m</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Louise Thys</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>23.12,34</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>288</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Marie Wærnes Blom</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>23.45,66</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>269</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aurora Aarflot Johannessen</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>29.48,26</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>136</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
